--- a/comparacion_configs.xlsx
+++ b/comparacion_configs.xlsx
@@ -510,22 +510,22 @@
         <v>26.2</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>279642</v>
+        <v>279776</v>
       </c>
       <c r="J2" t="n">
-        <v>56.4</v>
+        <v>56.44</v>
       </c>
       <c r="K2" t="n">
         <v>0.042</v>
       </c>
       <c r="L2" t="n">
-        <v>2526</v>
+        <v>2514</v>
       </c>
       <c r="M2" t="n">
-        <v>4320</v>
+        <v>4327</v>
       </c>
     </row>
     <row r="3">
@@ -555,22 +555,22 @@
         <v>3.5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>75234</v>
+        <v>75299</v>
       </c>
       <c r="J3" t="n">
-        <v>12.29</v>
+        <v>12.31</v>
       </c>
       <c r="K3" t="n">
-        <v>0.095</v>
+        <v>0.092</v>
       </c>
       <c r="L3" t="n">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="M3" t="n">
-        <v>7209</v>
+        <v>7228</v>
       </c>
     </row>
     <row r="4">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G4" t="n">
         <v>0.5</v>
@@ -603,19 +603,19 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>13381</v>
+        <v>13417</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.109</v>
+        <v>0.108</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4" t="n">
-        <v>755</v>
+        <v>405</v>
       </c>
     </row>
     <row r="5">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D5" t="n">
         <v>25</v>
@@ -639,7 +639,7 @@
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="G5" t="n">
         <v>0.6</v>
@@ -648,19 +648,19 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>14282</v>
+        <v>15246</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -687,25 +687,25 @@
         <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I6" t="n">
-        <v>216697</v>
+        <v>216267</v>
       </c>
       <c r="J6" t="n">
-        <v>51.24</v>
+        <v>51.11</v>
       </c>
       <c r="K6" t="n">
         <v>0.052</v>
       </c>
       <c r="L6" t="n">
-        <v>2131</v>
+        <v>2127</v>
       </c>
       <c r="M6" t="n">
-        <v>3068</v>
+        <v>3071</v>
       </c>
     </row>
     <row r="7">
@@ -735,22 +735,22 @@
         <v>2.1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>40233</v>
+        <v>40190</v>
       </c>
       <c r="J7" t="n">
-        <v>6.9</v>
+        <v>6.91</v>
       </c>
       <c r="K7" t="n">
-        <v>0.098</v>
+        <v>0.097</v>
       </c>
       <c r="L7" t="n">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="M7" t="n">
-        <v>3240</v>
+        <v>3220</v>
       </c>
     </row>
     <row r="8">
@@ -783,19 +783,19 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>13348</v>
+        <v>13371</v>
       </c>
       <c r="J8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="K8" t="n">
-        <v>0.108</v>
+        <v>0.106</v>
       </c>
       <c r="L8" t="n">
         <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D9" t="n">
         <v>25</v>
@@ -819,28 +819,28 @@
         <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>14641</v>
+        <v>15608</v>
       </c>
       <c r="J9" t="n">
         <v>0.04</v>
       </c>
       <c r="K9" t="n">
-        <v>0.108</v>
+        <v>0.106</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -873,16 +873,16 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>346815</v>
+        <v>346468</v>
       </c>
       <c r="J10" t="n">
-        <v>62.23</v>
+        <v>62.22</v>
       </c>
       <c r="K10" t="n">
-        <v>0.042</v>
+        <v>0.04</v>
       </c>
       <c r="L10" t="n">
-        <v>2657</v>
+        <v>2651</v>
       </c>
       <c r="M10" t="n">
         <v>3312</v>
@@ -915,22 +915,22 @@
         <v>5.5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>127163</v>
+        <v>126918</v>
       </c>
       <c r="J11" t="n">
-        <v>20.86</v>
+        <v>20.87</v>
       </c>
       <c r="K11" t="n">
-        <v>0.09</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="M11" t="n">
-        <v>4386</v>
+        <v>4373</v>
       </c>
     </row>
     <row r="12">
@@ -963,19 +963,19 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>21202</v>
+        <v>21175</v>
       </c>
       <c r="J12" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="K12" t="n">
-        <v>0.115</v>
+        <v>0.112</v>
       </c>
       <c r="L12" t="n">
         <v>59</v>
       </c>
       <c r="M12" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -1008,19 +1008,19 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>22979</v>
+        <v>22943</v>
       </c>
       <c r="J13" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="K13" t="n">
-        <v>0.115</v>
+        <v>0.112</v>
       </c>
       <c r="L13" t="n">
         <v>58</v>
       </c>
       <c r="M13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
